--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="78">
   <si>
     <t>subsector</t>
   </si>
@@ -42,6 +42,174 @@
   </si>
   <si>
     <t>min_55</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t>Economy</t>
@@ -469,181 +637,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -822,10 +990,10 @@
     </row>
     <row r="3" spans="1:65">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1004,10 +1172,10 @@
     </row>
     <row r="4" spans="1:65">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1186,10 +1354,10 @@
     </row>
     <row r="5" spans="1:65">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1368,10 +1536,10 @@
     </row>
     <row r="6" spans="1:65">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1550,10 +1718,10 @@
     </row>
     <row r="7" spans="1:65">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1732,10 +1900,10 @@
     </row>
     <row r="8" spans="1:65">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1914,10 +2082,10 @@
     </row>
     <row r="9" spans="1:65">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2096,10 +2264,10 @@
     </row>
     <row r="10" spans="1:65">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2278,10 +2446,10 @@
     </row>
     <row r="11" spans="1:65">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2460,10 +2628,10 @@
     </row>
     <row r="12" spans="1:65">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2678,181 +2846,181 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1">
-        <v>1</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1">
-        <v>4</v>
-      </c>
-      <c r="O1" s="1">
-        <v>5</v>
-      </c>
-      <c r="P1" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>7</v>
-      </c>
-      <c r="R1" s="1">
-        <v>8</v>
-      </c>
-      <c r="S1" s="1">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:65">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="H2">
         <v>1</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="strategy_id-0" sheetId="1" r:id="rId1"/>
-    <sheet name="strategy_id-6002" sheetId="2" r:id="rId2"/>
+    <sheet name="strategy_id-6004" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,16 +23,16 @@
     <t>variable</t>
   </si>
   <si>
+    <t>normalize_group</t>
+  </si>
+  <si>
+    <t>trajgroup_no_vary_q</t>
+  </si>
+  <si>
+    <t>uniform_scaling_q</t>
+  </si>
+  <si>
     <t>variable_trajectory_group</t>
-  </si>
-  <si>
-    <t>normalize_group</t>
-  </si>
-  <si>
-    <t>trajgroup_no_vary_q</t>
-  </si>
-  <si>
-    <t>uniform_scaling_q</t>
   </si>
   <si>
     <t>variable_trajectory_group_trajectory_type</t>
@@ -844,148 +844,148 @@
         <v>107.73</v>
       </c>
       <c r="R2">
-        <v>114.019334432094</v>
+        <v>113.4839020740705</v>
       </c>
       <c r="S2">
-        <v>122.1078961975356</v>
+        <v>120.4064201005888</v>
       </c>
       <c r="T2">
-        <v>132.3039055300299</v>
+        <v>128.3532438272277</v>
       </c>
       <c r="U2">
-        <v>143.3082828724901</v>
+        <v>137.7872072485289</v>
       </c>
       <c r="V2">
-        <v>155.1813741084759</v>
+        <v>150.2569495045207</v>
       </c>
       <c r="W2">
-        <v>167.9877170067779</v>
+        <v>165.0121819458647</v>
       </c>
       <c r="X2">
-        <v>181.796307344735</v>
+        <v>182.0909427772617</v>
       </c>
       <c r="Y2">
-        <v>196.6854249162688</v>
+        <v>200.5367552805983</v>
       </c>
       <c r="Z2">
-        <v>212.7349555894364</v>
+        <v>217.2175521884183</v>
       </c>
       <c r="AA2">
-        <v>230.0303074788577</v>
+        <v>235.1759656162268</v>
       </c>
       <c r="AB2">
-        <v>248.6627623846451</v>
+        <v>254.500095980128</v>
       </c>
       <c r="AC2">
-        <v>268.729847309086</v>
+        <v>275.2832989371603</v>
       </c>
       <c r="AD2">
-        <v>290.2873556602208</v>
+        <v>297.6300049364239</v>
       </c>
       <c r="AE2">
-        <v>313.4348694005669</v>
+        <v>321.6461852948495</v>
       </c>
       <c r="AF2">
-        <v>338.2777171492559</v>
+        <v>347.4440325228045</v>
       </c>
       <c r="AG2">
-        <v>364.9272357062743</v>
+        <v>375.142250384756</v>
       </c>
       <c r="AH2">
-        <v>393.5010382620756</v>
+        <v>404.8663518336542</v>
       </c>
       <c r="AI2">
-        <v>422.1029423003247</v>
+        <v>434.6185505985255</v>
       </c>
       <c r="AJ2">
-        <v>450.4139896446107</v>
+        <v>464.0590568509459</v>
       </c>
       <c r="AK2">
-        <v>478.0951465510552</v>
+        <v>492.8265323695617</v>
       </c>
       <c r="AL2">
-        <v>504.7933455205991</v>
+        <v>520.5446906897764</v>
       </c>
       <c r="AM2">
-        <v>530.1483941327481</v>
+        <v>546.8298498045566</v>
       </c>
       <c r="AN2">
-        <v>553.8005860595561</v>
+        <v>571.2992524250106</v>
       </c>
       <c r="AO2">
-        <v>575.3988089158787</v>
+        <v>593.5799232695859</v>
       </c>
       <c r="AP2">
-        <v>596.7461047266578</v>
+        <v>615.6017384228875</v>
       </c>
       <c r="AQ2">
-        <v>617.7515676130361</v>
+        <v>637.2709196153731</v>
       </c>
       <c r="AR2">
-        <v>638.3226948145502</v>
+        <v>658.4920412385651</v>
       </c>
       <c r="AS2">
-        <v>658.3660274317272</v>
+        <v>679.1686913334561</v>
       </c>
       <c r="AT2">
-        <v>677.7878252409631</v>
+        <v>699.2041677277932</v>
       </c>
       <c r="AU2">
-        <v>696.4947692176138</v>
+        <v>718.5022027570803</v>
       </c>
       <c r="AV2">
-        <v>714.3946847865064</v>
+        <v>736.9677093679373</v>
       </c>
       <c r="AW2">
-        <v>731.3972782844253</v>
+        <v>754.5075408508942</v>
       </c>
       <c r="AX2">
-        <v>747.4148786788542</v>
+        <v>771.0312559955288</v>
       </c>
       <c r="AY2">
-        <v>762.3631762524312</v>
+        <v>786.4518811154394</v>
       </c>
       <c r="AZ2">
-        <v>777.6104397774799</v>
+        <v>802.1809187377484</v>
       </c>
       <c r="BA2">
-        <v>793.1626485730295</v>
+        <v>818.2245371125033</v>
       </c>
       <c r="BB2">
-        <v>809.0259015444904</v>
+        <v>834.5890278547536</v>
       </c>
       <c r="BC2">
-        <v>825.2064195753803</v>
+        <v>851.2808084118489</v>
       </c>
       <c r="BD2">
-        <v>841.7105479668879</v>
+        <v>868.3064245800858</v>
       </c>
       <c r="BE2">
-        <v>858.5447589262259</v>
+        <v>885.6725530716878</v>
       </c>
       <c r="BF2">
-        <v>875.7156541047507</v>
+        <v>903.386004133122</v>
       </c>
       <c r="BG2">
-        <v>893.2299671868457</v>
+        <v>921.4537242157844</v>
       </c>
       <c r="BH2">
-        <v>911.0945665305826</v>
+        <v>939.8827987001</v>
       </c>
       <c r="BI2">
-        <v>929.3164578611944</v>
+        <v>958.680454674102</v>
       </c>
       <c r="BJ2">
-        <v>947.9027870184182</v>
+        <v>977.854063767584</v>
       </c>
       <c r="BK2">
-        <v>966.8608427587864</v>
+        <v>997.4111450429356</v>
       </c>
       <c r="BL2">
-        <v>986.1980596139624</v>
+        <v>1017.359367943795</v>
       </c>
       <c r="BM2">
-        <v>1005.922020806242</v>
+        <v>1037.706555302671</v>
       </c>
     </row>
     <row r="3" spans="1:65">
@@ -2458,172 +2458,172 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>27415805</v>
+        <v>27658870</v>
       </c>
       <c r="K11">
-        <v>28126956</v>
+        <v>28190888</v>
       </c>
       <c r="L11">
-        <v>28903581</v>
+        <v>28730674</v>
       </c>
       <c r="M11">
-        <v>29672226</v>
+        <v>29278236</v>
       </c>
       <c r="N11">
-        <v>30457624</v>
+        <v>29833576</v>
       </c>
       <c r="O11">
-        <v>31243802</v>
+        <v>30396690</v>
       </c>
       <c r="P11">
-        <v>31996822</v>
+        <v>29782795</v>
       </c>
       <c r="Q11">
-        <v>32696899</v>
+        <v>29108697</v>
       </c>
       <c r="R11">
-        <v>33340889</v>
+        <v>28371445</v>
       </c>
       <c r="S11">
-        <v>33786906</v>
+        <v>27567973</v>
       </c>
       <c r="T11">
-        <v>34021897</v>
+        <v>26695088</v>
       </c>
       <c r="U11">
-        <v>34249768</v>
+        <v>27144192</v>
       </c>
       <c r="V11">
-        <v>34481269</v>
+        <v>27589779</v>
       </c>
       <c r="W11">
-        <v>34715860</v>
+        <v>28031343</v>
       </c>
       <c r="X11">
-        <v>34953184</v>
+        <v>28468369</v>
       </c>
       <c r="Y11">
-        <v>35203042</v>
+        <v>28900334</v>
       </c>
       <c r="Z11">
-        <v>35449905</v>
+        <v>29319581</v>
       </c>
       <c r="AA11">
-        <v>35698610</v>
+        <v>29731712</v>
       </c>
       <c r="AB11">
-        <v>35945186</v>
+        <v>30136140</v>
       </c>
       <c r="AC11">
-        <v>36190509</v>
+        <v>30532274</v>
       </c>
       <c r="AD11">
-        <v>36438468</v>
+        <v>30919515</v>
       </c>
       <c r="AE11">
-        <v>36687216</v>
+        <v>31299409</v>
       </c>
       <c r="AF11">
-        <v>36935757</v>
+        <v>31669306</v>
       </c>
       <c r="AG11">
-        <v>37182833</v>
+        <v>32028593</v>
       </c>
       <c r="AH11">
-        <v>37420691</v>
+        <v>32376659</v>
       </c>
       <c r="AI11">
-        <v>37650711</v>
+        <v>32712885</v>
       </c>
       <c r="AJ11">
-        <v>37877765</v>
+        <v>33040657</v>
       </c>
       <c r="AK11">
-        <v>38095266</v>
+        <v>33292065</v>
       </c>
       <c r="AL11">
-        <v>38298536</v>
+        <v>33530248</v>
       </c>
       <c r="AM11">
-        <v>38482596</v>
+        <v>33752950</v>
       </c>
       <c r="AN11">
-        <v>38642590</v>
+        <v>33957313</v>
       </c>
       <c r="AO11">
-        <v>38769171</v>
+        <v>34131767</v>
       </c>
       <c r="AP11">
-        <v>38877625</v>
+        <v>34291200</v>
       </c>
       <c r="AQ11">
-        <v>38966634</v>
+        <v>34434227</v>
       </c>
       <c r="AR11">
-        <v>39030689</v>
+        <v>34557163</v>
       </c>
       <c r="AS11">
-        <v>39070478</v>
+        <v>34659707</v>
       </c>
       <c r="AT11">
-        <v>38932957</v>
+        <v>34744662</v>
       </c>
       <c r="AU11">
-        <v>38771038</v>
+        <v>34811457</v>
       </c>
       <c r="AV11">
-        <v>38585277</v>
+        <v>34860383</v>
       </c>
       <c r="AW11">
-        <v>38373283</v>
+        <v>34888823</v>
       </c>
       <c r="AX11">
-        <v>38134634</v>
+        <v>34894988</v>
       </c>
       <c r="AY11">
-        <v>37926252</v>
+        <v>34880806</v>
       </c>
       <c r="AZ11">
-        <v>37699152</v>
+        <v>34845998</v>
       </c>
       <c r="BA11">
-        <v>37453933</v>
+        <v>34790430</v>
       </c>
       <c r="BB11">
-        <v>37189594</v>
+        <v>34712361</v>
       </c>
       <c r="BC11">
-        <v>36905389</v>
+        <v>34609842</v>
       </c>
       <c r="BD11">
-        <v>36582189</v>
+        <v>34487747</v>
       </c>
       <c r="BE11">
-        <v>36245108</v>
+        <v>34345195</v>
       </c>
       <c r="BF11">
-        <v>35889776</v>
+        <v>34178397</v>
       </c>
       <c r="BG11">
-        <v>35518552</v>
+        <v>33988521</v>
       </c>
       <c r="BH11">
-        <v>35130850</v>
+        <v>33774814</v>
       </c>
       <c r="BI11">
-        <v>34702738</v>
+        <v>33539166</v>
       </c>
       <c r="BJ11">
-        <v>34260452</v>
+        <v>33280836</v>
       </c>
       <c r="BK11">
-        <v>33802517</v>
+        <v>32998979</v>
       </c>
       <c r="BL11">
-        <v>33327910</v>
+        <v>32693415</v>
       </c>
       <c r="BM11">
-        <v>32838868</v>
+        <v>32366147</v>
       </c>
     </row>
     <row r="12" spans="1:65">
@@ -2640,172 +2640,172 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>7922107</v>
+        <v>7933333</v>
       </c>
       <c r="K12">
-        <v>8404570</v>
+        <v>8421971</v>
       </c>
       <c r="L12">
-        <v>8925631</v>
+        <v>8932111</v>
       </c>
       <c r="M12">
-        <v>9464281</v>
+        <v>9464583</v>
       </c>
       <c r="N12">
-        <v>10028890</v>
+        <v>10020248</v>
       </c>
       <c r="O12">
-        <v>10615042</v>
+        <v>10600000</v>
       </c>
       <c r="P12">
-        <v>11230833</v>
+        <v>12389532</v>
       </c>
       <c r="Q12">
-        <v>11850618</v>
+        <v>14272982</v>
       </c>
       <c r="R12">
-        <v>12471966</v>
+        <v>16254265</v>
       </c>
       <c r="S12">
-        <v>13038714</v>
+        <v>18337443</v>
       </c>
       <c r="T12">
-        <v>13539081</v>
+        <v>20526731</v>
       </c>
       <c r="U12">
-        <v>14066453</v>
+        <v>21418585</v>
       </c>
       <c r="V12">
-        <v>14609266</v>
+        <v>22338468</v>
       </c>
       <c r="W12">
-        <v>15167816</v>
+        <v>23286817</v>
       </c>
       <c r="X12">
-        <v>15742472</v>
+        <v>24264058</v>
       </c>
       <c r="Y12">
-        <v>16338317</v>
+        <v>25270602</v>
       </c>
       <c r="Z12">
-        <v>16958971</v>
+        <v>26313971</v>
       </c>
       <c r="AA12">
-        <v>17597617</v>
+        <v>27387256</v>
       </c>
       <c r="AB12">
-        <v>18252830</v>
+        <v>28490768</v>
       </c>
       <c r="AC12">
-        <v>18925503</v>
+        <v>29624796</v>
       </c>
       <c r="AD12">
-        <v>19618225</v>
+        <v>30789608</v>
       </c>
       <c r="AE12">
-        <v>20327606</v>
+        <v>31983296</v>
       </c>
       <c r="AF12">
-        <v>21056609</v>
+        <v>33208124</v>
       </c>
       <c r="AG12">
-        <v>21805102</v>
+        <v>34464285</v>
       </c>
       <c r="AH12">
-        <v>22568977</v>
+        <v>35751944</v>
       </c>
       <c r="AI12">
-        <v>23349288</v>
+        <v>37071243</v>
       </c>
       <c r="AJ12">
-        <v>24143637</v>
+        <v>38418290</v>
       </c>
       <c r="AK12">
-        <v>24953718</v>
+        <v>39721241</v>
       </c>
       <c r="AL12">
-        <v>25776584</v>
+        <v>41052256</v>
       </c>
       <c r="AM12">
-        <v>26608744</v>
+        <v>42409142</v>
       </c>
       <c r="AN12">
-        <v>27446418</v>
+        <v>43788670</v>
       </c>
       <c r="AO12">
-        <v>28301495</v>
+        <v>45205953</v>
       </c>
       <c r="AP12">
-        <v>29165895</v>
+        <v>46652125</v>
       </c>
       <c r="AQ12">
-        <v>30038289</v>
+        <v>48125905</v>
       </c>
       <c r="AR12">
-        <v>30913903</v>
+        <v>49622540</v>
       </c>
       <c r="AS12">
-        <v>31792509</v>
+        <v>51141720</v>
       </c>
       <c r="AT12">
-        <v>32831784</v>
+        <v>52684229</v>
       </c>
       <c r="AU12">
-        <v>33879628</v>
+        <v>54252964</v>
       </c>
       <c r="AV12">
-        <v>34935745</v>
+        <v>55848803</v>
       </c>
       <c r="AW12">
-        <v>35997090</v>
+        <v>57467914</v>
       </c>
       <c r="AX12">
-        <v>37062154</v>
+        <v>59107416</v>
       </c>
       <c r="AY12">
-        <v>38078839</v>
+        <v>60766424</v>
       </c>
       <c r="AZ12">
-        <v>39102900</v>
+        <v>62448465</v>
       </c>
       <c r="BA12">
-        <v>40134406</v>
+        <v>64153424</v>
       </c>
       <c r="BB12">
-        <v>41171700</v>
+        <v>65878121</v>
       </c>
       <c r="BC12">
-        <v>42213232</v>
+        <v>67618588</v>
       </c>
       <c r="BD12">
-        <v>43288336</v>
+        <v>69379317</v>
       </c>
       <c r="BE12">
-        <v>44374670</v>
+        <v>71163265</v>
       </c>
       <c r="BF12">
-        <v>45466544</v>
+        <v>72962516</v>
       </c>
       <c r="BG12">
-        <v>46566308</v>
+        <v>74779078</v>
       </c>
       <c r="BH12">
-        <v>47672690</v>
+        <v>76610878</v>
       </c>
       <c r="BI12">
-        <v>48811245</v>
+        <v>78456193</v>
       </c>
       <c r="BJ12">
-        <v>49959641</v>
+        <v>80318217</v>
       </c>
       <c r="BK12">
-        <v>51115365</v>
+        <v>82194435</v>
       </c>
       <c r="BL12">
-        <v>52276252</v>
+        <v>84083731</v>
       </c>
       <c r="BM12">
-        <v>53445148</v>
+        <v>85990676</v>
       </c>
     </row>
   </sheetData>
@@ -3068,133 +3068,133 @@
         <v>0.88</v>
       </c>
       <c r="W2">
-        <v>0.8613953488372093</v>
+        <v>0.8660465116279069</v>
       </c>
       <c r="X2">
-        <v>0.8432558139534885</v>
+        <v>0.8525581395348838</v>
       </c>
       <c r="Y2">
-        <v>0.8255813953488371</v>
+        <v>0.8395348837209302</v>
       </c>
       <c r="Z2">
-        <v>0.8083720930232559</v>
+        <v>0.8269767441860466</v>
       </c>
       <c r="AA2">
-        <v>0.7916279069767441</v>
+        <v>0.8148837209302325</v>
       </c>
       <c r="AB2">
-        <v>0.7753488372093023</v>
+        <v>0.8032558139534883</v>
       </c>
       <c r="AC2">
-        <v>0.7595348837209303</v>
+        <v>0.792093023255814</v>
       </c>
       <c r="AD2">
-        <v>0.7441860465116279</v>
+        <v>0.7813953488372094</v>
       </c>
       <c r="AE2">
-        <v>0.7293023255813953</v>
+        <v>0.7711627906976743</v>
       </c>
       <c r="AF2">
-        <v>0.7148837209302326</v>
+        <v>0.7613953488372093</v>
       </c>
       <c r="AG2">
-        <v>0.7009302325581396</v>
+        <v>0.752093023255814</v>
       </c>
       <c r="AH2">
-        <v>0.6874418604651162</v>
+        <v>0.7432558139534883</v>
       </c>
       <c r="AI2">
-        <v>0.6744186046511629</v>
+        <v>0.7348837209302326</v>
       </c>
       <c r="AJ2">
-        <v>0.6618604651162791</v>
+        <v>0.7269767441860465</v>
       </c>
       <c r="AK2">
-        <v>0.6497674418604651</v>
+        <v>0.7195348837209302</v>
       </c>
       <c r="AL2">
-        <v>0.6381395348837209</v>
+        <v>0.7125581395348837</v>
       </c>
       <c r="AM2">
-        <v>0.6269767441860464</v>
+        <v>0.7060465116279069</v>
       </c>
       <c r="AN2">
-        <v>0.6162790697674418</v>
+        <v>0.7</v>
       </c>
       <c r="AO2">
-        <v>0.6116279069767442</v>
+        <v>0.7</v>
       </c>
       <c r="AP2">
-        <v>0.6069767441860465</v>
+        <v>0.7</v>
       </c>
       <c r="AQ2">
-        <v>0.6023255813953488</v>
+        <v>0.7</v>
       </c>
       <c r="AR2">
-        <v>0.5976744186046512</v>
+        <v>0.7</v>
       </c>
       <c r="AS2">
-        <v>0.5930232558139534</v>
+        <v>0.7</v>
       </c>
       <c r="AT2">
-        <v>0.5883720930232558</v>
+        <v>0.7</v>
       </c>
       <c r="AU2">
-        <v>0.5837209302325581</v>
+        <v>0.7</v>
       </c>
       <c r="AV2">
-        <v>0.5790697674418605</v>
+        <v>0.7</v>
       </c>
       <c r="AW2">
-        <v>0.5744186046511628</v>
+        <v>0.7</v>
       </c>
       <c r="AX2">
-        <v>0.5697674418604651</v>
+        <v>0.7</v>
       </c>
       <c r="AY2">
-        <v>0.5651162790697675</v>
+        <v>0.7</v>
       </c>
       <c r="AZ2">
-        <v>0.5604651162790697</v>
+        <v>0.7</v>
       </c>
       <c r="BA2">
-        <v>0.5558139534883721</v>
+        <v>0.7</v>
       </c>
       <c r="BB2">
-        <v>0.5511627906976744</v>
+        <v>0.7</v>
       </c>
       <c r="BC2">
-        <v>0.5465116279069767</v>
+        <v>0.7</v>
       </c>
       <c r="BD2">
-        <v>0.5418604651162791</v>
+        <v>0.7</v>
       </c>
       <c r="BE2">
-        <v>0.5372093023255814</v>
+        <v>0.7</v>
       </c>
       <c r="BF2">
-        <v>0.5325581395348837</v>
+        <v>0.7</v>
       </c>
       <c r="BG2">
-        <v>0.5279069767441861</v>
+        <v>0.7</v>
       </c>
       <c r="BH2">
-        <v>0.5232558139534884</v>
+        <v>0.7</v>
       </c>
       <c r="BI2">
-        <v>0.5186046511627908</v>
+        <v>0.7</v>
       </c>
       <c r="BJ2">
-        <v>0.513953488372093</v>
+        <v>0.7</v>
       </c>
       <c r="BK2">
-        <v>0.5093023255813953</v>
+        <v>0.7</v>
       </c>
       <c r="BL2">
-        <v>0.5046511627906977</v>
+        <v>0.7</v>
       </c>
       <c r="BM2">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
@@ -3068,133 +3068,133 @@
         <v>0.88</v>
       </c>
       <c r="W2">
-        <v>0.8660465116279069</v>
+        <v>0.8613953488372093</v>
       </c>
       <c r="X2">
-        <v>0.8525581395348838</v>
+        <v>0.8432558139534885</v>
       </c>
       <c r="Y2">
-        <v>0.8395348837209302</v>
+        <v>0.8255813953488371</v>
       </c>
       <c r="Z2">
-        <v>0.8269767441860466</v>
+        <v>0.8083720930232559</v>
       </c>
       <c r="AA2">
-        <v>0.8148837209302325</v>
+        <v>0.7916279069767441</v>
       </c>
       <c r="AB2">
-        <v>0.8032558139534883</v>
+        <v>0.7753488372093023</v>
       </c>
       <c r="AC2">
-        <v>0.792093023255814</v>
+        <v>0.7595348837209303</v>
       </c>
       <c r="AD2">
-        <v>0.7813953488372094</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="AE2">
-        <v>0.7711627906976743</v>
+        <v>0.7293023255813953</v>
       </c>
       <c r="AF2">
-        <v>0.7613953488372093</v>
+        <v>0.7148837209302326</v>
       </c>
       <c r="AG2">
-        <v>0.752093023255814</v>
+        <v>0.7009302325581396</v>
       </c>
       <c r="AH2">
-        <v>0.7432558139534883</v>
+        <v>0.6874418604651162</v>
       </c>
       <c r="AI2">
-        <v>0.7348837209302326</v>
+        <v>0.6744186046511629</v>
       </c>
       <c r="AJ2">
-        <v>0.7269767441860465</v>
+        <v>0.6618604651162791</v>
       </c>
       <c r="AK2">
-        <v>0.7195348837209302</v>
+        <v>0.6497674418604651</v>
       </c>
       <c r="AL2">
-        <v>0.7125581395348837</v>
+        <v>0.6381395348837209</v>
       </c>
       <c r="AM2">
-        <v>0.7060465116279069</v>
+        <v>0.6269767441860464</v>
       </c>
       <c r="AN2">
-        <v>0.7</v>
+        <v>0.6162790697674418</v>
       </c>
       <c r="AO2">
-        <v>0.7</v>
+        <v>0.6116279069767442</v>
       </c>
       <c r="AP2">
-        <v>0.7</v>
+        <v>0.6069767441860465</v>
       </c>
       <c r="AQ2">
-        <v>0.7</v>
+        <v>0.6023255813953488</v>
       </c>
       <c r="AR2">
-        <v>0.7</v>
+        <v>0.5976744186046512</v>
       </c>
       <c r="AS2">
-        <v>0.7</v>
+        <v>0.5930232558139534</v>
       </c>
       <c r="AT2">
-        <v>0.7</v>
+        <v>0.5883720930232558</v>
       </c>
       <c r="AU2">
-        <v>0.7</v>
+        <v>0.5837209302325581</v>
       </c>
       <c r="AV2">
-        <v>0.7</v>
+        <v>0.5790697674418605</v>
       </c>
       <c r="AW2">
-        <v>0.7</v>
+        <v>0.5744186046511628</v>
       </c>
       <c r="AX2">
-        <v>0.7</v>
+        <v>0.5697674418604651</v>
       </c>
       <c r="AY2">
-        <v>0.7</v>
+        <v>0.5651162790697675</v>
       </c>
       <c r="AZ2">
-        <v>0.7</v>
+        <v>0.5604651162790697</v>
       </c>
       <c r="BA2">
-        <v>0.7</v>
+        <v>0.5558139534883721</v>
       </c>
       <c r="BB2">
-        <v>0.7</v>
+        <v>0.5511627906976744</v>
       </c>
       <c r="BC2">
-        <v>0.7</v>
+        <v>0.5465116279069767</v>
       </c>
       <c r="BD2">
-        <v>0.7</v>
+        <v>0.5418604651162791</v>
       </c>
       <c r="BE2">
-        <v>0.7</v>
+        <v>0.5372093023255814</v>
       </c>
       <c r="BF2">
-        <v>0.7</v>
+        <v>0.5325581395348837</v>
       </c>
       <c r="BG2">
-        <v>0.7</v>
+        <v>0.5279069767441861</v>
       </c>
       <c r="BH2">
-        <v>0.7</v>
+        <v>0.5232558139534884</v>
       </c>
       <c r="BI2">
-        <v>0.7</v>
+        <v>0.5186046511627908</v>
       </c>
       <c r="BJ2">
-        <v>0.7</v>
+        <v>0.513953488372093</v>
       </c>
       <c r="BK2">
-        <v>0.7</v>
+        <v>0.5093023255813953</v>
       </c>
       <c r="BL2">
-        <v>0.7</v>
+        <v>0.5046511627906977</v>
       </c>
       <c r="BM2">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
@@ -3068,130 +3068,130 @@
         <v>0.88</v>
       </c>
       <c r="W2">
-        <v>0.8613953488372093</v>
+        <v>0.8594285714285713</v>
       </c>
       <c r="X2">
-        <v>0.8432558139534885</v>
+        <v>0.8394285714285714</v>
       </c>
       <c r="Y2">
-        <v>0.8255813953488371</v>
+        <v>0.82</v>
       </c>
       <c r="Z2">
-        <v>0.8083720930232559</v>
+        <v>0.8011428571428572</v>
       </c>
       <c r="AA2">
-        <v>0.7916279069767441</v>
+        <v>0.7828571428571428</v>
       </c>
       <c r="AB2">
-        <v>0.7753488372093023</v>
+        <v>0.7651428571428571</v>
       </c>
       <c r="AC2">
-        <v>0.7595348837209303</v>
+        <v>0.7480000000000001</v>
       </c>
       <c r="AD2">
-        <v>0.7441860465116279</v>
+        <v>0.7314285714285715</v>
       </c>
       <c r="AE2">
-        <v>0.7293023255813953</v>
+        <v>0.7154285714285714</v>
       </c>
       <c r="AF2">
-        <v>0.7148837209302326</v>
+        <v>0.7</v>
       </c>
       <c r="AG2">
-        <v>0.7009302325581396</v>
+        <v>0.6851428571428572</v>
       </c>
       <c r="AH2">
-        <v>0.6874418604651162</v>
+        <v>0.6708571428571428</v>
       </c>
       <c r="AI2">
-        <v>0.6744186046511629</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="AJ2">
-        <v>0.6618604651162791</v>
+        <v>0.644</v>
       </c>
       <c r="AK2">
-        <v>0.6497674418604651</v>
+        <v>0.6314285714285713</v>
       </c>
       <c r="AL2">
-        <v>0.6381395348837209</v>
+        <v>0.6194285714285714</v>
       </c>
       <c r="AM2">
-        <v>0.6269767441860464</v>
+        <v>0.608</v>
       </c>
       <c r="AN2">
-        <v>0.6162790697674418</v>
+        <v>0.5971428571428572</v>
       </c>
       <c r="AO2">
-        <v>0.6116279069767442</v>
+        <v>0.5914285714285714</v>
       </c>
       <c r="AP2">
-        <v>0.6069767441860465</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="AQ2">
-        <v>0.6023255813953488</v>
+        <v>0.58</v>
       </c>
       <c r="AR2">
-        <v>0.5976744186046512</v>
+        <v>0.5742857142857143</v>
       </c>
       <c r="AS2">
-        <v>0.5930232558139534</v>
+        <v>0.5685714285714285</v>
       </c>
       <c r="AT2">
-        <v>0.5883720930232558</v>
+        <v>0.5628571428571428</v>
       </c>
       <c r="AU2">
-        <v>0.5837209302325581</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="AV2">
-        <v>0.5790697674418605</v>
+        <v>0.5514285714285714</v>
       </c>
       <c r="AW2">
-        <v>0.5744186046511628</v>
+        <v>0.5457142857142857</v>
       </c>
       <c r="AX2">
-        <v>0.5697674418604651</v>
+        <v>0.54</v>
       </c>
       <c r="AY2">
-        <v>0.5651162790697675</v>
+        <v>0.5342857142857143</v>
       </c>
       <c r="AZ2">
-        <v>0.5604651162790697</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="BA2">
-        <v>0.5558139534883721</v>
+        <v>0.5228571428571429</v>
       </c>
       <c r="BB2">
-        <v>0.5511627906976744</v>
+        <v>0.5171428571428571</v>
       </c>
       <c r="BC2">
-        <v>0.5465116279069767</v>
+        <v>0.5114285714285715</v>
       </c>
       <c r="BD2">
-        <v>0.5418604651162791</v>
+        <v>0.5057142857142857</v>
       </c>
       <c r="BE2">
-        <v>0.5372093023255814</v>
+        <v>0.5</v>
       </c>
       <c r="BF2">
-        <v>0.5325581395348837</v>
+        <v>0.5</v>
       </c>
       <c r="BG2">
-        <v>0.5279069767441861</v>
+        <v>0.5</v>
       </c>
       <c r="BH2">
-        <v>0.5232558139534884</v>
+        <v>0.5</v>
       </c>
       <c r="BI2">
-        <v>0.5186046511627908</v>
+        <v>0.5</v>
       </c>
       <c r="BJ2">
-        <v>0.513953488372093</v>
+        <v>0.5</v>
       </c>
       <c r="BK2">
-        <v>0.5093023255813953</v>
+        <v>0.5</v>
       </c>
       <c r="BL2">
-        <v>0.5046511627906977</v>
+        <v>0.5</v>
       </c>
       <c r="BM2">
         <v>0.5</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
@@ -23,6 +23,9 @@
     <t>variable</t>
   </si>
   <si>
+    <t>variable_trajectory_group</t>
+  </si>
+  <si>
     <t>normalize_group</t>
   </si>
   <si>
@@ -30,9 +33,6 @@
   </si>
   <si>
     <t>uniform_scaling_q</t>
-  </si>
-  <si>
-    <t>variable_trajectory_group</t>
   </si>
   <si>
     <t>variable_trajectory_group_trajectory_type</t>
@@ -813,11 +813,14 @@
       <c r="B2" t="s">
         <v>67</v>
       </c>
+      <c r="C2">
+        <v>62</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J2">
         <v>79.03</v>
@@ -1181,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1541,6 +1544,9 @@
       <c r="B6" t="s">
         <v>71</v>
       </c>
+      <c r="C6">
+        <v>29</v>
+      </c>
       <c r="H6">
         <v>1</v>
       </c>
@@ -2451,11 +2457,14 @@
       <c r="B11" t="s">
         <v>76</v>
       </c>
+      <c r="C11">
+        <v>65</v>
+      </c>
       <c r="H11">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="J11">
         <v>27658870</v>
@@ -2633,11 +2642,14 @@
       <c r="B12" t="s">
         <v>77</v>
       </c>
+      <c r="C12">
+        <v>65</v>
+      </c>
       <c r="H12">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="J12">
         <v>7933333</v>
@@ -3022,6 +3034,9 @@
       <c r="B2" t="s">
         <v>71</v>
       </c>
+      <c r="C2">
+        <v>29</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
@@ -814,7 +814,7 @@
         <v>67</v>
       </c>
       <c r="C2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -2458,7 +2458,7 @@
         <v>76</v>
       </c>
       <c r="C11">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11">
         <v>1.05</v>
@@ -2643,7 +2643,7 @@
         <v>77</v>
       </c>
       <c r="C12">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H12">
         <v>1.05</v>

--- a/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
+++ b/data_processing/transformations/templates/calibrated/uganda/model_input_variables_uganda_se_calibrated.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="strategy_id-0" sheetId="1" r:id="rId1"/>
-    <sheet name="strategy_id-6004" sheetId="2" r:id="rId2"/>
+    <sheet name="strategy_id-6007" sheetId="2" r:id="rId2"/>
+    <sheet name="strategy_id-6063" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="78">
   <si>
     <t>subsector</t>
   </si>
@@ -814,7 +815,7 @@
         <v>67</v>
       </c>
       <c r="C2">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1544,9 +1545,6 @@
       <c r="B6" t="s">
         <v>71</v>
       </c>
-      <c r="C6">
-        <v>27</v>
-      </c>
       <c r="H6">
         <v>1</v>
       </c>
@@ -2458,7 +2456,7 @@
         <v>76</v>
       </c>
       <c r="C11">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H11">
         <v>1.05</v>
@@ -2643,7 +2641,7 @@
         <v>77</v>
       </c>
       <c r="C12">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="H12">
         <v>1.05</v>
@@ -3034,8 +3032,394 @@
       <c r="B2" t="s">
         <v>71</v>
       </c>
-      <c r="C2">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>0.98</v>
+      </c>
+      <c r="Y2">
+        <v>0.96</v>
+      </c>
+      <c r="Z2">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AA2">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.9</v>
+      </c>
+      <c r="AC2">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="AF2">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>0.8</v>
+      </c>
+      <c r="AH2">
+        <v>0.78</v>
+      </c>
+      <c r="AI2">
+        <v>0.76</v>
+      </c>
+      <c r="AJ2">
+        <v>0.74</v>
+      </c>
+      <c r="AK2">
+        <v>0.72</v>
+      </c>
+      <c r="AL2">
+        <v>0.7</v>
+      </c>
+      <c r="AM2">
+        <v>0.68</v>
+      </c>
+      <c r="AN2">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AO2">
+        <v>0.64</v>
+      </c>
+      <c r="AP2">
+        <v>0.62</v>
+      </c>
+      <c r="AQ2">
+        <v>0.6</v>
+      </c>
+      <c r="AR2">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AS2">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AT2">
+        <v>0.54</v>
+      </c>
+      <c r="AU2">
+        <v>0.52</v>
+      </c>
+      <c r="AV2">
+        <v>0.5</v>
+      </c>
+      <c r="AW2">
+        <v>0.48</v>
+      </c>
+      <c r="AX2">
+        <v>0.46</v>
+      </c>
+      <c r="AY2">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>0.4199999999999999</v>
+      </c>
+      <c r="BA2">
+        <v>0.4</v>
+      </c>
+      <c r="BB2">
+        <v>0.38</v>
+      </c>
+      <c r="BC2">
+        <v>0.36</v>
+      </c>
+      <c r="BD2">
+        <v>0.34</v>
+      </c>
+      <c r="BE2">
+        <v>0.32</v>
+      </c>
+      <c r="BF2">
+        <v>0.3</v>
+      </c>
+      <c r="BG2">
+        <v>0.3</v>
+      </c>
+      <c r="BH2">
+        <v>0.3</v>
+      </c>
+      <c r="BI2">
+        <v>0.3</v>
+      </c>
+      <c r="BJ2">
+        <v>0.3</v>
+      </c>
+      <c r="BK2">
+        <v>0.3</v>
+      </c>
+      <c r="BL2">
+        <v>0.3</v>
+      </c>
+      <c r="BM2">
+        <v>0.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BM2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:65">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
       </c>
       <c r="H2">
         <v>1</v>
